--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedAufnehmenBundleKA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedAufnehmenBundleKA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T09:14:27+00:00</t>
+    <t>2026-05-05T07:22:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedAufnehmenBundleKA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedAufnehmenBundleKA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T07:22:12+00:00</t>
+    <t>2026-05-15T07:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedAufnehmenBundleKA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedAufnehmenBundleKA.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T07:39:15+00:00</t>
+    <t>2026-05-15T09:26:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -999,7 +999,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Patient {https://elga.moped.at/StructureDefinition/MopedPatient}
+    <t xml:space="preserve">Patient {https://elga.moped.at/StructureDefinition/MopedBasisPatientvbPK|https://elga.moped.at/StructureDefinition/MopedBasisPatientKlarname}
 </t>
   </si>
   <si>
@@ -2526,7 +2526,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="112.83984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="116.8828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedAufnehmenBundleKA.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedAufnehmenBundleKA.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13757" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13758" uniqueCount="715">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T09:26:31+00:00</t>
+    <t>2026-05-22T08:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1335,8 +1335,21 @@
     <t>Bundle.entry:Entbindung.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Observation
+    <t>Vital Signs
+MeasurementResultsTests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observation {https://elga.moped.at/StructureDefinition/MopedObservationGeburtenanzahl|https://elga.moped.at/StructureDefinition/MopedObservationEntbindungsart}
 </t>
+  </si>
+  <si>
+    <t>Measurements and simple assertions</t>
+  </si>
+  <si>
+    <t>Measurements and simple assertions made about a patient, device or other subject.</t>
+  </si>
+  <si>
+    <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
   </si>
   <si>
     <t>Bundle.entry:Entbindung.search</t>
@@ -2526,7 +2539,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="116.8828125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="133.94921875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -20990,7 +21003,7 @@
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>20</v>
+        <v>422</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -21006,18 +21019,20 @@
         <v>20</v>
       </c>
       <c r="J183" t="s" s="2">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>187</v>
+        <v>424</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N183" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="N183" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
         <v>20</v>
@@ -21075,7 +21090,7 @@
         <v>80</v>
       </c>
       <c r="AI183" t="s" s="2">
-        <v>189</v>
+        <v>20</v>
       </c>
       <c r="AJ183" t="s" s="2">
         <v>20</v>
@@ -21083,7 +21098,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>190</v>
@@ -21183,7 +21198,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>194</v>
@@ -21283,7 +21298,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>195</v>
@@ -21385,7 +21400,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>196</v>
@@ -21489,7 +21504,7 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>197</v>
@@ -21591,7 +21606,7 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>203</v>
@@ -21693,7 +21708,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>208</v>
@@ -21793,7 +21808,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>212</v>
@@ -21893,7 +21908,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>213</v>
@@ -21995,7 +22010,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>214</v>
@@ -22099,7 +22114,7 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>215</v>
@@ -22197,7 +22212,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>221</v>
@@ -22299,7 +22314,7 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>225</v>
@@ -22399,7 +22414,7 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>228</v>
@@ -22499,7 +22514,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>231</v>
@@ -22599,7 +22614,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>234</v>
@@ -22699,7 +22714,7 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>237</v>
@@ -22799,7 +22814,7 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>241</v>
@@ -22899,7 +22914,7 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>242</v>
@@ -23001,7 +23016,7 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>243</v>
@@ -23105,7 +23120,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>244</v>
@@ -23205,7 +23220,7 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>247</v>
@@ -23305,7 +23320,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>250</v>
@@ -23407,7 +23422,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>254</v>
@@ -23509,7 +23524,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>258</v>
@@ -23611,13 +23626,13 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B209" t="s" s="2">
         <v>167</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D209" t="s" s="2">
         <v>20</v>
@@ -23642,7 +23657,7 @@
         <v>135</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="M209" t="s" s="2">
         <v>170</v>
@@ -23713,7 +23728,7 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B210" t="s" s="2">
         <v>174</v>
@@ -23813,7 +23828,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>175</v>
@@ -23915,7 +23930,7 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B212" t="s" s="2">
         <v>176</v>
@@ -24019,7 +24034,7 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B213" t="s" s="2">
         <v>177</v>
@@ -24119,7 +24134,7 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B214" t="s" s="2">
         <v>180</v>
@@ -24221,7 +24236,7 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B215" t="s" s="2">
         <v>185</v>
@@ -24247,7 +24262,7 @@
         <v>20</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="L215" t="s" s="2">
         <v>272</v>
@@ -24321,7 +24336,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>190</v>
@@ -24421,7 +24436,7 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B217" t="s" s="2">
         <v>194</v>
@@ -24521,7 +24536,7 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B218" t="s" s="2">
         <v>195</v>
@@ -24623,7 +24638,7 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B219" t="s" s="2">
         <v>196</v>
@@ -24727,7 +24742,7 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B220" t="s" s="2">
         <v>197</v>
@@ -24829,7 +24844,7 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B221" t="s" s="2">
         <v>203</v>
@@ -24931,7 +24946,7 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B222" t="s" s="2">
         <v>208</v>
@@ -25031,7 +25046,7 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B223" t="s" s="2">
         <v>212</v>
@@ -25131,7 +25146,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B224" t="s" s="2">
         <v>213</v>
@@ -25233,7 +25248,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B225" t="s" s="2">
         <v>214</v>
@@ -25337,7 +25352,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B226" t="s" s="2">
         <v>215</v>
@@ -25435,7 +25450,7 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>221</v>
@@ -25537,7 +25552,7 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B228" t="s" s="2">
         <v>225</v>
@@ -25637,7 +25652,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>228</v>
@@ -25737,7 +25752,7 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B230" t="s" s="2">
         <v>231</v>
@@ -25837,7 +25852,7 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B231" t="s" s="2">
         <v>234</v>
@@ -25937,7 +25952,7 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B232" t="s" s="2">
         <v>237</v>
@@ -26037,7 +26052,7 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B233" t="s" s="2">
         <v>241</v>
@@ -26137,7 +26152,7 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B234" t="s" s="2">
         <v>242</v>
@@ -26239,7 +26254,7 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B235" t="s" s="2">
         <v>243</v>
@@ -26343,7 +26358,7 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B236" t="s" s="2">
         <v>244</v>
@@ -26443,7 +26458,7 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B237" t="s" s="2">
         <v>247</v>
@@ -26543,7 +26558,7 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B238" t="s" s="2">
         <v>250</v>
@@ -26645,7 +26660,7 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B239" t="s" s="2">
         <v>254</v>
@@ -26747,7 +26762,7 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B240" t="s" s="2">
         <v>258</v>
@@ -26849,13 +26864,13 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B241" t="s" s="2">
         <v>167</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D241" t="s" s="2">
         <v>20</v>
@@ -26951,7 +26966,7 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B242" t="s" s="2">
         <v>174</v>
@@ -27051,7 +27066,7 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B243" t="s" s="2">
         <v>175</v>
@@ -27153,7 +27168,7 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B244" t="s" s="2">
         <v>176</v>
@@ -27257,7 +27272,7 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B245" t="s" s="2">
         <v>177</v>
@@ -27357,7 +27372,7 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B246" t="s" s="2">
         <v>180</v>
@@ -27459,7 +27474,7 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B247" t="s" s="2">
         <v>185</v>
@@ -27485,16 +27500,16 @@
         <v>20</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="N247" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="O247" s="2"/>
       <c r="P247" t="s" s="2">
@@ -27561,7 +27576,7 @@
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B248" t="s" s="2">
         <v>190</v>
@@ -27661,7 +27676,7 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B249" t="s" s="2">
         <v>194</v>
@@ -27761,7 +27776,7 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B250" t="s" s="2">
         <v>195</v>
@@ -27863,7 +27878,7 @@
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B251" t="s" s="2">
         <v>196</v>
@@ -27967,7 +27982,7 @@
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B252" t="s" s="2">
         <v>197</v>
@@ -28069,7 +28084,7 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B253" t="s" s="2">
         <v>203</v>
@@ -28171,7 +28186,7 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B254" t="s" s="2">
         <v>208</v>
@@ -28271,7 +28286,7 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B255" t="s" s="2">
         <v>212</v>
@@ -28371,7 +28386,7 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B256" t="s" s="2">
         <v>213</v>
@@ -28473,7 +28488,7 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B257" t="s" s="2">
         <v>214</v>
@@ -28577,7 +28592,7 @@
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B258" t="s" s="2">
         <v>215</v>
@@ -28675,7 +28690,7 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B259" t="s" s="2">
         <v>221</v>
@@ -28777,7 +28792,7 @@
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B260" t="s" s="2">
         <v>225</v>
@@ -28877,7 +28892,7 @@
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B261" t="s" s="2">
         <v>228</v>
@@ -28977,7 +28992,7 @@
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B262" t="s" s="2">
         <v>231</v>
@@ -29077,7 +29092,7 @@
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B263" t="s" s="2">
         <v>234</v>
@@ -29177,7 +29192,7 @@
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B264" t="s" s="2">
         <v>237</v>
@@ -29277,7 +29292,7 @@
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B265" t="s" s="2">
         <v>241</v>
@@ -29377,7 +29392,7 @@
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B266" t="s" s="2">
         <v>242</v>
@@ -29479,7 +29494,7 @@
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B267" t="s" s="2">
         <v>243</v>
@@ -29583,7 +29598,7 @@
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B268" t="s" s="2">
         <v>244</v>
@@ -29683,7 +29698,7 @@
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B269" t="s" s="2">
         <v>247</v>
@@ -29783,7 +29798,7 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B270" t="s" s="2">
         <v>250</v>
@@ -29885,7 +29900,7 @@
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B271" t="s" s="2">
         <v>254</v>
@@ -29987,7 +30002,7 @@
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B272" t="s" s="2">
         <v>258</v>
@@ -30089,13 +30104,13 @@
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B273" t="s" s="2">
         <v>167</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D273" t="s" s="2">
         <v>20</v>
@@ -30191,7 +30206,7 @@
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B274" t="s" s="2">
         <v>174</v>
@@ -30291,7 +30306,7 @@
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B275" t="s" s="2">
         <v>175</v>
@@ -30393,7 +30408,7 @@
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B276" t="s" s="2">
         <v>176</v>
@@ -30497,7 +30512,7 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B277" t="s" s="2">
         <v>177</v>
@@ -30597,7 +30612,7 @@
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B278" t="s" s="2">
         <v>180</v>
@@ -30699,7 +30714,7 @@
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B279" t="s" s="2">
         <v>185</v>
@@ -30725,13 +30740,13 @@
         <v>20</v>
       </c>
       <c r="K279" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="M279" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="N279" s="2"/>
       <c r="O279" s="2"/>
@@ -30799,7 +30814,7 @@
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B280" t="s" s="2">
         <v>190</v>
@@ -30899,7 +30914,7 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B281" t="s" s="2">
         <v>194</v>
@@ -30999,7 +31014,7 @@
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B282" t="s" s="2">
         <v>195</v>
@@ -31101,7 +31116,7 @@
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B283" t="s" s="2">
         <v>196</v>
@@ -31205,7 +31220,7 @@
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B284" t="s" s="2">
         <v>197</v>
@@ -31307,7 +31322,7 @@
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B285" t="s" s="2">
         <v>203</v>
@@ -31409,7 +31424,7 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B286" t="s" s="2">
         <v>208</v>
@@ -31509,7 +31524,7 @@
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B287" t="s" s="2">
         <v>212</v>
@@ -31609,7 +31624,7 @@
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="B288" t="s" s="2">
         <v>213</v>
@@ -31711,7 +31726,7 @@
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B289" t="s" s="2">
         <v>214</v>
@@ -31815,7 +31830,7 @@
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B290" t="s" s="2">
         <v>215</v>
@@ -31913,7 +31928,7 @@
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B291" t="s" s="2">
         <v>221</v>
@@ -32015,7 +32030,7 @@
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B292" t="s" s="2">
         <v>225</v>
@@ -32115,7 +32130,7 @@
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B293" t="s" s="2">
         <v>228</v>
@@ -32215,7 +32230,7 @@
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B294" t="s" s="2">
         <v>231</v>
@@ -32315,7 +32330,7 @@
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B295" t="s" s="2">
         <v>234</v>
@@ -32415,7 +32430,7 @@
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B296" t="s" s="2">
         <v>237</v>
@@ -32515,7 +32530,7 @@
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B297" t="s" s="2">
         <v>241</v>
@@ -32615,7 +32630,7 @@
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B298" t="s" s="2">
         <v>242</v>
@@ -32717,7 +32732,7 @@
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B299" t="s" s="2">
         <v>243</v>
@@ -32821,7 +32836,7 @@
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B300" t="s" s="2">
         <v>244</v>
@@ -32921,7 +32936,7 @@
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B301" t="s" s="2">
         <v>247</v>
@@ -33021,7 +33036,7 @@
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B302" t="s" s="2">
         <v>250</v>
@@ -33123,7 +33138,7 @@
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B303" t="s" s="2">
         <v>254</v>
@@ -33225,7 +33240,7 @@
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B304" t="s" s="2">
         <v>258</v>
@@ -33327,13 +33342,13 @@
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B305" t="s" s="2">
         <v>167</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="D305" t="s" s="2">
         <v>20</v>
@@ -33429,7 +33444,7 @@
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B306" t="s" s="2">
         <v>174</v>
@@ -33529,7 +33544,7 @@
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B307" t="s" s="2">
         <v>175</v>
@@ -33631,7 +33646,7 @@
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B308" t="s" s="2">
         <v>176</v>
@@ -33735,7 +33750,7 @@
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B309" t="s" s="2">
         <v>177</v>
@@ -33835,7 +33850,7 @@
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B310" t="s" s="2">
         <v>180</v>
@@ -33937,7 +33952,7 @@
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B311" t="s" s="2">
         <v>185</v>
@@ -33963,13 +33978,13 @@
         <v>20</v>
       </c>
       <c r="K311" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="L311" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="M311" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="N311" s="2"/>
       <c r="O311" s="2"/>
@@ -34037,7 +34052,7 @@
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B312" t="s" s="2">
         <v>190</v>
@@ -34137,7 +34152,7 @@
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="B313" t="s" s="2">
         <v>194</v>
@@ -34237,7 +34252,7 @@
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B314" t="s" s="2">
         <v>195</v>
@@ -34339,7 +34354,7 @@
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B315" t="s" s="2">
         <v>196</v>
@@ -34443,7 +34458,7 @@
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B316" t="s" s="2">
         <v>197</v>
@@ -34545,7 +34560,7 @@
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="B317" t="s" s="2">
         <v>203</v>
@@ -34647,7 +34662,7 @@
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B318" t="s" s="2">
         <v>208</v>
@@ -34747,7 +34762,7 @@
     </row>
     <row r="319">
       <c r="A319" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B319" t="s" s="2">
         <v>212</v>
@@ -34847,7 +34862,7 @@
     </row>
     <row r="320">
       <c r="A320" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B320" t="s" s="2">
         <v>213</v>
@@ -34949,7 +34964,7 @@
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B321" t="s" s="2">
         <v>214</v>
@@ -35053,7 +35068,7 @@
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B322" t="s" s="2">
         <v>215</v>
@@ -35151,7 +35166,7 @@
     </row>
     <row r="323">
       <c r="A323" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B323" t="s" s="2">
         <v>221</v>
@@ -35253,7 +35268,7 @@
     </row>
     <row r="324">
       <c r="A324" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B324" t="s" s="2">
         <v>225</v>
@@ -35353,7 +35368,7 @@
     </row>
     <row r="325">
       <c r="A325" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B325" t="s" s="2">
         <v>228</v>
@@ -35453,7 +35468,7 @@
     </row>
     <row r="326">
       <c r="A326" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B326" t="s" s="2">
         <v>231</v>
@@ -35553,7 +35568,7 @@
     </row>
     <row r="327">
       <c r="A327" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B327" t="s" s="2">
         <v>234</v>
@@ -35653,7 +35668,7 @@
     </row>
     <row r="328">
       <c r="A328" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B328" t="s" s="2">
         <v>237</v>
@@ -35753,7 +35768,7 @@
     </row>
     <row r="329">
       <c r="A329" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B329" t="s" s="2">
         <v>241</v>
@@ -35853,7 +35868,7 @@
     </row>
     <row r="330">
       <c r="A330" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B330" t="s" s="2">
         <v>242</v>
@@ -35955,7 +35970,7 @@
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B331" t="s" s="2">
         <v>243</v>
@@ -36059,7 +36074,7 @@
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B332" t="s" s="2">
         <v>244</v>
@@ -36159,7 +36174,7 @@
     </row>
     <row r="333">
       <c r="A333" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B333" t="s" s="2">
         <v>247</v>
@@ -36259,7 +36274,7 @@
     </row>
     <row r="334">
       <c r="A334" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B334" t="s" s="2">
         <v>250</v>
@@ -36361,7 +36376,7 @@
     </row>
     <row r="335">
       <c r="A335" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B335" t="s" s="2">
         <v>254</v>
@@ -36463,7 +36478,7 @@
     </row>
     <row r="336">
       <c r="A336" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B336" t="s" s="2">
         <v>258</v>
@@ -36565,13 +36580,13 @@
     </row>
     <row r="337">
       <c r="A337" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B337" t="s" s="2">
         <v>167</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="D337" t="s" s="2">
         <v>20</v>
@@ -36667,7 +36682,7 @@
     </row>
     <row r="338">
       <c r="A338" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B338" t="s" s="2">
         <v>174</v>
@@ -36767,7 +36782,7 @@
     </row>
     <row r="339">
       <c r="A339" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B339" t="s" s="2">
         <v>175</v>
@@ -36869,7 +36884,7 @@
     </row>
     <row r="340">
       <c r="A340" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B340" t="s" s="2">
         <v>176</v>
@@ -36973,7 +36988,7 @@
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B341" t="s" s="2">
         <v>177</v>
@@ -37073,7 +37088,7 @@
     </row>
     <row r="342">
       <c r="A342" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B342" t="s" s="2">
         <v>180</v>
@@ -37175,14 +37190,14 @@
     </row>
     <row r="343">
       <c r="A343" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B343" t="s" s="2">
         <v>185</v>
       </c>
       <c r="C343" s="2"/>
       <c r="D343" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="E343" s="2"/>
       <c r="F343" t="s" s="2">
@@ -37201,16 +37216,16 @@
         <v>20</v>
       </c>
       <c r="K343" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="L343" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="M343" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="N343" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="O343" s="2"/>
       <c r="P343" t="s" s="2">
@@ -37277,7 +37292,7 @@
     </row>
     <row r="344">
       <c r="A344" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="B344" t="s" s="2">
         <v>190</v>
@@ -37377,7 +37392,7 @@
     </row>
     <row r="345">
       <c r="A345" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B345" t="s" s="2">
         <v>194</v>
@@ -37477,7 +37492,7 @@
     </row>
     <row r="346">
       <c r="A346" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="B346" t="s" s="2">
         <v>195</v>
@@ -37579,7 +37594,7 @@
     </row>
     <row r="347">
       <c r="A347" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B347" t="s" s="2">
         <v>196</v>
@@ -37683,7 +37698,7 @@
     </row>
     <row r="348">
       <c r="A348" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="B348" t="s" s="2">
         <v>197</v>
@@ -37785,7 +37800,7 @@
     </row>
     <row r="349">
       <c r="A349" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B349" t="s" s="2">
         <v>203</v>
@@ -37887,7 +37902,7 @@
     </row>
     <row r="350">
       <c r="A350" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B350" t="s" s="2">
         <v>208</v>
@@ -37987,7 +38002,7 @@
     </row>
     <row r="351">
       <c r="A351" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B351" t="s" s="2">
         <v>212</v>
@@ -38087,7 +38102,7 @@
     </row>
     <row r="352">
       <c r="A352" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="B352" t="s" s="2">
         <v>213</v>
@@ -38189,7 +38204,7 @@
     </row>
     <row r="353">
       <c r="A353" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B353" t="s" s="2">
         <v>214</v>
@@ -38293,7 +38308,7 @@
     </row>
     <row r="354">
       <c r="A354" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="B354" t="s" s="2">
         <v>215</v>
@@ -38391,7 +38406,7 @@
     </row>
     <row r="355">
       <c r="A355" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B355" t="s" s="2">
         <v>221</v>
@@ -38493,7 +38508,7 @@
     </row>
     <row r="356">
       <c r="A356" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="B356" t="s" s="2">
         <v>225</v>
@@ -38593,7 +38608,7 @@
     </row>
     <row r="357">
       <c r="A357" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B357" t="s" s="2">
         <v>228</v>
@@ -38693,7 +38708,7 @@
     </row>
     <row r="358">
       <c r="A358" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="B358" t="s" s="2">
         <v>231</v>
@@ -38793,7 +38808,7 @@
     </row>
     <row r="359">
       <c r="A359" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="B359" t="s" s="2">
         <v>234</v>
@@ -38893,7 +38908,7 @@
     </row>
     <row r="360">
       <c r="A360" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="B360" t="s" s="2">
         <v>237</v>
@@ -38993,7 +39008,7 @@
     </row>
     <row r="361">
       <c r="A361" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="B361" t="s" s="2">
         <v>241</v>
@@ -39093,7 +39108,7 @@
     </row>
     <row r="362">
       <c r="A362" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B362" t="s" s="2">
         <v>242</v>
@@ -39195,7 +39210,7 @@
     </row>
     <row r="363">
       <c r="A363" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="B363" t="s" s="2">
         <v>243</v>
@@ -39299,7 +39314,7 @@
     </row>
     <row r="364">
       <c r="A364" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="B364" t="s" s="2">
         <v>244</v>
@@ -39399,7 +39414,7 @@
     </row>
     <row r="365">
       <c r="A365" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B365" t="s" s="2">
         <v>247</v>
@@ -39499,7 +39514,7 @@
     </row>
     <row r="366">
       <c r="A366" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="B366" t="s" s="2">
         <v>250</v>
@@ -39601,7 +39616,7 @@
     </row>
     <row r="367">
       <c r="A367" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B367" t="s" s="2">
         <v>254</v>
@@ -39703,7 +39718,7 @@
     </row>
     <row r="368">
       <c r="A368" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B368" t="s" s="2">
         <v>258</v>
@@ -39805,13 +39820,13 @@
     </row>
     <row r="369">
       <c r="A369" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B369" t="s" s="2">
         <v>167</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="D369" t="s" s="2">
         <v>20</v>
@@ -39907,7 +39922,7 @@
     </row>
     <row r="370">
       <c r="A370" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B370" t="s" s="2">
         <v>174</v>
@@ -40007,7 +40022,7 @@
     </row>
     <row r="371">
       <c r="A371" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="B371" t="s" s="2">
         <v>175</v>
@@ -40109,7 +40124,7 @@
     </row>
     <row r="372">
       <c r="A372" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="B372" t="s" s="2">
         <v>176</v>
@@ -40213,7 +40228,7 @@
     </row>
     <row r="373">
       <c r="A373" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="B373" t="s" s="2">
         <v>177</v>
@@ -40313,7 +40328,7 @@
     </row>
     <row r="374">
       <c r="A374" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="B374" t="s" s="2">
         <v>180</v>
@@ -40415,7 +40430,7 @@
     </row>
     <row r="375">
       <c r="A375" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="B375" t="s" s="2">
         <v>185</v>
@@ -40441,7 +40456,7 @@
         <v>81</v>
       </c>
       <c r="K375" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="L375" t="s" s="2">
         <v>187</v>
@@ -40515,7 +40530,7 @@
     </row>
     <row r="376">
       <c r="A376" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="B376" t="s" s="2">
         <v>190</v>
@@ -40615,7 +40630,7 @@
     </row>
     <row r="377">
       <c r="A377" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B377" t="s" s="2">
         <v>194</v>
@@ -40715,7 +40730,7 @@
     </row>
     <row r="378">
       <c r="A378" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="B378" t="s" s="2">
         <v>195</v>
@@ -40817,7 +40832,7 @@
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="B379" t="s" s="2">
         <v>196</v>
@@ -40921,7 +40936,7 @@
     </row>
     <row r="380">
       <c r="A380" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="B380" t="s" s="2">
         <v>197</v>
@@ -41023,7 +41038,7 @@
     </row>
     <row r="381">
       <c r="A381" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B381" t="s" s="2">
         <v>203</v>
@@ -41125,7 +41140,7 @@
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="B382" t="s" s="2">
         <v>208</v>
@@ -41225,7 +41240,7 @@
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B383" t="s" s="2">
         <v>212</v>
@@ -41325,7 +41340,7 @@
     </row>
     <row r="384">
       <c r="A384" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B384" t="s" s="2">
         <v>213</v>
@@ -41427,7 +41442,7 @@
     </row>
     <row r="385">
       <c r="A385" t="s" s="2">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="B385" t="s" s="2">
         <v>214</v>
@@ -41531,7 +41546,7 @@
     </row>
     <row r="386">
       <c r="A386" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="B386" t="s" s="2">
         <v>215</v>
@@ -41594,7 +41609,7 @@
       </c>
       <c r="Y386" s="2"/>
       <c r="Z386" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="AA386" t="s" s="2">
         <v>20</v>
@@ -41629,7 +41644,7 @@
     </row>
     <row r="387">
       <c r="A387" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="B387" t="s" s="2">
         <v>221</v>
@@ -41731,7 +41746,7 @@
     </row>
     <row r="388">
       <c r="A388" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B388" t="s" s="2">
         <v>225</v>
@@ -41831,7 +41846,7 @@
     </row>
     <row r="389">
       <c r="A389" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="B389" t="s" s="2">
         <v>228</v>
@@ -41931,7 +41946,7 @@
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="B390" t="s" s="2">
         <v>231</v>
@@ -42031,7 +42046,7 @@
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="B391" t="s" s="2">
         <v>234</v>
@@ -42131,7 +42146,7 @@
     </row>
     <row r="392">
       <c r="A392" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="B392" t="s" s="2">
         <v>237</v>
@@ -42231,7 +42246,7 @@
     </row>
     <row r="393">
       <c r="A393" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="B393" t="s" s="2">
         <v>241</v>
@@ -42331,7 +42346,7 @@
     </row>
     <row r="394">
       <c r="A394" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="B394" t="s" s="2">
         <v>242</v>
@@ -42433,7 +42448,7 @@
     </row>
     <row r="395">
       <c r="A395" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B395" t="s" s="2">
         <v>243</v>
@@ -42537,7 +42552,7 @@
     </row>
     <row r="396">
       <c r="A396" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="B396" t="s" s="2">
         <v>244</v>
@@ -42637,7 +42652,7 @@
     </row>
     <row r="397">
       <c r="A397" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B397" t="s" s="2">
         <v>247</v>
@@ -42737,7 +42752,7 @@
     </row>
     <row r="398">
       <c r="A398" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="B398" t="s" s="2">
         <v>250</v>
@@ -42839,7 +42854,7 @@
     </row>
     <row r="399">
       <c r="A399" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B399" t="s" s="2">
         <v>254</v>
@@ -42941,7 +42956,7 @@
     </row>
     <row r="400">
       <c r="A400" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="B400" t="s" s="2">
         <v>258</v>
@@ -43043,13 +43058,13 @@
     </row>
     <row r="401">
       <c r="A401" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="B401" t="s" s="2">
         <v>167</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="D401" t="s" s="2">
         <v>20</v>
@@ -43145,7 +43160,7 @@
     </row>
     <row r="402">
       <c r="A402" t="s" s="2">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="B402" t="s" s="2">
         <v>174</v>
@@ -43245,7 +43260,7 @@
     </row>
     <row r="403">
       <c r="A403" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="B403" t="s" s="2">
         <v>175</v>
@@ -43347,7 +43362,7 @@
     </row>
     <row r="404">
       <c r="A404" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="B404" t="s" s="2">
         <v>176</v>
@@ -43451,7 +43466,7 @@
     </row>
     <row r="405">
       <c r="A405" t="s" s="2">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="B405" t="s" s="2">
         <v>177</v>
@@ -43551,7 +43566,7 @@
     </row>
     <row r="406">
       <c r="A406" t="s" s="2">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="B406" t="s" s="2">
         <v>180</v>
@@ -43653,7 +43668,7 @@
     </row>
     <row r="407">
       <c r="A407" t="s" s="2">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="B407" t="s" s="2">
         <v>185</v>
@@ -43679,7 +43694,7 @@
         <v>81</v>
       </c>
       <c r="K407" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="L407" t="s" s="2">
         <v>187</v>
@@ -43753,7 +43768,7 @@
     </row>
     <row r="408">
       <c r="A408" t="s" s="2">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="B408" t="s" s="2">
         <v>190</v>
@@ -43853,7 +43868,7 @@
     </row>
     <row r="409">
       <c r="A409" t="s" s="2">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="B409" t="s" s="2">
         <v>194</v>
@@ -43953,7 +43968,7 @@
     </row>
     <row r="410">
       <c r="A410" t="s" s="2">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="B410" t="s" s="2">
         <v>195</v>
@@ -44055,7 +44070,7 @@
     </row>
     <row r="411">
       <c r="A411" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B411" t="s" s="2">
         <v>196</v>
@@ -44159,7 +44174,7 @@
     </row>
     <row r="412">
       <c r="A412" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="B412" t="s" s="2">
         <v>197</v>
@@ -44261,7 +44276,7 @@
     </row>
     <row r="413">
       <c r="A413" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="B413" t="s" s="2">
         <v>203</v>
@@ -44363,7 +44378,7 @@
     </row>
     <row r="414">
       <c r="A414" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="B414" t="s" s="2">
         <v>208</v>
@@ -44463,7 +44478,7 @@
     </row>
     <row r="415">
       <c r="A415" t="s" s="2">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="B415" t="s" s="2">
         <v>212</v>
@@ -44563,7 +44578,7 @@
     </row>
     <row r="416">
       <c r="A416" t="s" s="2">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="B416" t="s" s="2">
         <v>213</v>
@@ -44665,7 +44680,7 @@
     </row>
     <row r="417">
       <c r="A417" t="s" s="2">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B417" t="s" s="2">
         <v>214</v>
@@ -44769,7 +44784,7 @@
     </row>
     <row r="418">
       <c r="A418" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="B418" t="s" s="2">
         <v>215</v>
@@ -44832,7 +44847,7 @@
       </c>
       <c r="Y418" s="2"/>
       <c r="Z418" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="AA418" t="s" s="2">
         <v>20</v>
@@ -44867,7 +44882,7 @@
     </row>
     <row r="419">
       <c r="A419" t="s" s="2">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="B419" t="s" s="2">
         <v>221</v>
@@ -44969,7 +44984,7 @@
     </row>
     <row r="420">
       <c r="A420" t="s" s="2">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="B420" t="s" s="2">
         <v>225</v>
@@ -45069,7 +45084,7 @@
     </row>
     <row r="421">
       <c r="A421" t="s" s="2">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="B421" t="s" s="2">
         <v>228</v>
@@ -45169,7 +45184,7 @@
     </row>
     <row r="422">
       <c r="A422" t="s" s="2">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="B422" t="s" s="2">
         <v>231</v>
@@ -45269,7 +45284,7 @@
     </row>
     <row r="423">
       <c r="A423" t="s" s="2">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="B423" t="s" s="2">
         <v>234</v>
@@ -45369,7 +45384,7 @@
     </row>
     <row r="424">
       <c r="A424" t="s" s="2">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="B424" t="s" s="2">
         <v>237</v>
@@ -45469,7 +45484,7 @@
     </row>
     <row r="425">
       <c r="A425" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="B425" t="s" s="2">
         <v>241</v>
@@ -45569,7 +45584,7 @@
     </row>
     <row r="426">
       <c r="A426" t="s" s="2">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="B426" t="s" s="2">
         <v>242</v>
@@ -45671,7 +45686,7 @@
     </row>
     <row r="427">
       <c r="A427" t="s" s="2">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="B427" t="s" s="2">
         <v>243</v>
@@ -45775,7 +45790,7 @@
     </row>
     <row r="428">
       <c r="A428" t="s" s="2">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="B428" t="s" s="2">
         <v>244</v>
@@ -45875,7 +45890,7 @@
     </row>
     <row r="429">
       <c r="A429" t="s" s="2">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="B429" t="s" s="2">
         <v>247</v>
@@ -45975,7 +45990,7 @@
     </row>
     <row r="430">
       <c r="A430" t="s" s="2">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="B430" t="s" s="2">
         <v>250</v>
@@ -46077,7 +46092,7 @@
     </row>
     <row r="431">
       <c r="A431" t="s" s="2">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="B431" t="s" s="2">
         <v>254</v>
@@ -46179,7 +46194,7 @@
     </row>
     <row r="432">
       <c r="A432" t="s" s="2">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="B432" t="s" s="2">
         <v>258</v>
@@ -46281,10 +46296,10 @@
     </row>
     <row r="433">
       <c r="A433" t="s" s="2">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C433" s="2"/>
       <c r="D433" t="s" s="2">
@@ -46307,19 +46322,19 @@
         <v>81</v>
       </c>
       <c r="K433" t="s" s="2">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="L433" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="M433" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="N433" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="O433" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="P433" t="s" s="2">
         <v>20</v>
@@ -46368,7 +46383,7 @@
         <v>20</v>
       </c>
       <c r="AF433" t="s" s="2">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="AG433" t="s" s="2">
         <v>73</v>
@@ -46385,10 +46400,10 @@
     </row>
     <row r="434">
       <c r="A434" t="s" s="2">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="B434" t="s" s="2">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="C434" s="2"/>
       <c r="D434" t="s" s="2">
@@ -46411,16 +46426,16 @@
         <v>81</v>
       </c>
       <c r="K434" t="s" s="2">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="L434" t="s" s="2">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="M434" t="s" s="2">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="N434" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="O434" s="2"/>
       <c r="P434" t="s" s="2">
@@ -46470,7 +46485,7 @@
         <v>20</v>
       </c>
       <c r="AF434" t="s" s="2">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="AG434" t="s" s="2">
         <v>73</v>
@@ -46479,7 +46494,7 @@
         <v>80</v>
       </c>
       <c r="AI434" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="AJ434" t="s" s="2">
         <v>20</v>
